--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:48:59+00:00</t>
+    <t>2026-04-25T16:59:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:59:12+00:00</t>
+    <t>2026-04-25T17:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:20:31+00:00</t>
+    <t>2026-04-25T17:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:34:35+00:00</t>
+    <t>2026-04-25T21:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ATTCK2FHIR IG</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ATTCK2FHIR IG (https://constir1.github.io/ATTCK2FHIR)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:04:27+00:00</t>
+    <t>2026-04-25T21:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:17:05+00:00</t>
+    <t>2026-04-25T21:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:19:40+00:00</t>
+    <t>2026-04-25T21:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fsh/ValueSet/MITRE-ATTCK-Tactics</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Tactics</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:21:24+00:00</t>
+    <t>2026-04-26T14:57:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -186,7 +186,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://attack.mitre.org</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/CodeSystem/MITRE-ATTCK-Tactics</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T14:57:42+00:00</t>
+    <t>2026-04-26T15:13:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:13:50+00:00</t>
+    <t>2026-04-26T15:44:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.3</t>
+    <t>0.0.04</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:44:08+00:00</t>
+    <t>2026-04-26T15:55:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.04</t>
+    <t>0.0.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:55:31+00:00</t>
+    <t>2026-04-26T20:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -30,12 +30,15 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.5</t>
+    <t>0.0.6</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>MITREATTCKTactics</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -57,19 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T20:36:59+00:00</t>
+    <t>2026-05-14T08:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
     <t>ATTCK2FHIR IG</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ATTCK2FHIR IG (https://constir1.github.io/ATTCK2FHIR)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -320,7 +317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -355,71 +352,71 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
         <v>22</v>
       </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -431,14 +428,8 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
+      <c r="B14" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -457,138 +448,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.6</t>
+    <t>0.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:02:20+00:00</t>
+    <t>2026-05-14T08:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -30,13 +30,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.7</t>
+    <t>0.0.8</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>MITREATTCKTactics</t>
+    <t>MITREATTCKTacticsVS</t>
   </si>
   <si>
     <t>Title</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:13:13+00:00</t>
+    <t>2026-05-14T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>All MITRE ATT&amp;CK Enterprise Tactics</t>
+    <t>All MITRE ATT&amp;CK Enterprise Tactics, imported from the MITRE-ATTCK-Tactics CodeSystem.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,91 +93,10 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>TA0006</t>
-  </si>
-  <si>
-    <t>Credential Access</t>
-  </si>
-  <si>
-    <t>TA0002</t>
-  </si>
-  <si>
-    <t>Execution</t>
-  </si>
-  <si>
-    <t>TA0040</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>TA0003</t>
-  </si>
-  <si>
-    <t>Persistence</t>
-  </si>
-  <si>
-    <t>TA0004</t>
-  </si>
-  <si>
-    <t>Privilege Escalation</t>
-  </si>
-  <si>
-    <t>TA0008</t>
-  </si>
-  <si>
-    <t>Lateral Movement</t>
-  </si>
-  <si>
-    <t>TA0005</t>
-  </si>
-  <si>
-    <t>Defense Evasion</t>
-  </si>
-  <si>
-    <t>TA0010</t>
-  </si>
-  <si>
-    <t>Exfiltration</t>
-  </si>
-  <si>
-    <t>TA0007</t>
-  </si>
-  <si>
-    <t>Discovery</t>
-  </si>
-  <si>
-    <t>TA0009</t>
-  </si>
-  <si>
-    <t>Collection</t>
-  </si>
-  <si>
-    <t>TA0042</t>
-  </si>
-  <si>
-    <t>Resource Development</t>
-  </si>
-  <si>
-    <t>TA0043</t>
-  </si>
-  <si>
-    <t>Reconnaissance</t>
-  </si>
-  <si>
-    <t>TA0011</t>
-  </si>
-  <si>
-    <t>Command and Control</t>
-  </si>
-  <si>
-    <t>TA0001</t>
-  </si>
-  <si>
-    <t>Initial Access</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
@@ -439,7 +358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -450,136 +369,26 @@
       <c r="A1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>28</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.8</t>
+    <t>0.0.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T10:01:26+00:00</t>
+    <t>2026-05-14T18:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.9</t>
+    <t>0.0.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T18:17:12+00:00</t>
+    <t>2026-05-15T18:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T18:07:37+00:00</t>
+    <t>2026-05-16T09:46:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Tactics.xlsx
+++ b/ValueSet-MITRE-ATTCK-Tactics.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.12</t>
+    <t>0.0.13</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T09:46:24+00:00</t>
+    <t>2026-05-16T09:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
